--- a/output/pdf_financials_xlsx/ROK.xlsx
+++ b/output/pdf_financials_xlsx/ROK.xlsx
@@ -7421,19 +7421,19 @@
         <v>-0.260212</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>-0.327321</v>
+        <v>0.184086</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>0.428417</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>0.388172</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="119">
@@ -8960,7 +8960,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>-</t>
@@ -12613,7 +12617,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -14209,7 +14217,11 @@
           <t>Prepaids and deposits 1,144,672</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -28134,7 +28146,11 @@
           <t>Exploration and evaluation expense (Note 6)</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -31221,7 +31237,11 @@
           <t>Exploration and evaluation expense (Note 7)</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -33332,7 +33352,11 @@
           <t>Exploration and evaluation expense (Note 7)</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
@@ -35831,7 +35855,11 @@
           <t>Exploration and evaluation expense</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ROK.xlsx
+++ b/output/pdf_financials_xlsx/ROK.xlsx
@@ -1089,19 +1089,19 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000404</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000113</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.057125</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.107</v>
       </c>
     </row>
     <row r="13">
@@ -2037,19 +2037,19 @@
         <v>-1.202882</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-2.316717</v>
+        <v>-2.316313</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>78.43811100000001</v>
+        <v>78.43822400000001</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-11.884907</v>
+        <v>-11.827782</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.709</v>
+        <v>-0.701</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-14.291</v>
+        <v>-14.184</v>
       </c>
     </row>
     <row r="28">
@@ -2153,19 +2153,19 @@
         <v>-0.943346</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.557043</v>
+        <v>-1.556639</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>97.628923</v>
+        <v>97.629036</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>11.395878</v>
+        <v>11.453003</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>22.093</v>
+        <v>22.101</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>4.887</v>
+        <v>4.994</v>
       </c>
     </row>
     <row r="30">
@@ -2223,7 +2223,7 @@
         <v>-205.480371079498</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-55.60571955278094</v>
+        <v>-55.59129174911763</v>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
@@ -7787,13 +7787,13 @@
         <v>0</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.05508</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.142</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.145</v>
       </c>
     </row>
     <row r="125">
@@ -7845,13 +7845,13 @@
         <v>0</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.05508</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.142</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.145</v>
       </c>
     </row>
     <row r="126">
@@ -30023,7 +30023,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -63654,7 +63658,7 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
@@ -63755,7 +63759,7 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
@@ -64060,7 +64064,7 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
@@ -67058,7 +67062,7 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
@@ -67264,7 +67268,7 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
@@ -68971,7 +68975,7 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
@@ -69177,7 +69181,7 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">

--- a/output/pdf_financials_xlsx/ROK.xlsx
+++ b/output/pdf_financials_xlsx/ROK.xlsx
@@ -1144,22 +1144,22 @@
         <v>-0</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.017823</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>-0</v>
+        <v>-1.103884</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>-0</v>
+        <v>-15.35324</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>-0</v>
+        <v>-15.320482</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>-0</v>
+        <v>-7.01</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>-0</v>
+        <v>-4.478</v>
       </c>
     </row>
     <row r="14">
@@ -2034,22 +2034,22 @@
         <v>-0.562889</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.202882</v>
+        <v>-1.185059</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-2.316313</v>
+        <v>-1.212429</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>78.43822400000001</v>
+        <v>93.791464</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-11.827782</v>
+        <v>3.4927</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.701</v>
+        <v>6.309</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-14.184</v>
+        <v>-9.706</v>
       </c>
     </row>
     <row r="28">
@@ -2150,22 +2150,22 @@
         <v>-0.562889</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.943346</v>
+        <v>-0.925523</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.556639</v>
+        <v>-0.452755</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>97.629036</v>
+        <v>112.982276</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>11.453003</v>
+        <v>26.773485</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>22.101</v>
+        <v>29.111</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>4.994</v>
+        <v>9.472</v>
       </c>
     </row>
     <row r="30">
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-205.480371079498</v>
+        <v>-201.5981511371334</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-55.59129174911763</v>
+        <v>-16.1689610088606</v>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
@@ -62761,7 +62761,11 @@
           <t>Net finance expense (Note 13)</t>
         </is>
       </c>
-      <c r="D542" t="inlineStr"/>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E542" t="inlineStr">
         <is>
           <t>-</t>
@@ -64357,7 +64361,11 @@
           <t>Total net finance expense</t>
         </is>
       </c>
-      <c r="D558" t="inlineStr"/>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E558" t="inlineStr">
         <is>
           <t>-</t>
@@ -67567,7 +67575,11 @@
           <t>Total net finance expense</t>
         </is>
       </c>
-      <c r="D590" t="inlineStr"/>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E590" t="inlineStr">
         <is>
           <t>-</t>
@@ -68268,7 +68280,11 @@
           <t>Net finance expense (Note 17)</t>
         </is>
       </c>
-      <c r="D597" t="inlineStr"/>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E597" t="inlineStr">
         <is>
           <t>-</t>
@@ -69480,7 +69496,11 @@
           <t>Total net finance expense</t>
         </is>
       </c>
-      <c r="D609" t="inlineStr"/>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E609" t="inlineStr">
         <is>
           <t>-</t>
@@ -70082,7 +70102,11 @@
           <t>Net finance expense</t>
         </is>
       </c>
-      <c r="D615" t="inlineStr"/>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E615" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ROK.xlsx
+++ b/output/pdf_financials_xlsx/ROK.xlsx
@@ -1606,13 +1606,13 @@
         <v>-9.526535000000001</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>-0.8058650000000001</v>
+        <v>-1.520596</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-0.340736</v>
+        <v>-0.41803</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-0.505928</v>
+        <v>-0.389877</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>-0.562889</v>
@@ -1664,10 +1664,10 @@
         <v>0</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>0.714731</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0</v>
+        <v>0.077294</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
         <v>0</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>59.454228</v>
       </c>
       <c r="F56" s="3" t="n">
         <v>0</v>
@@ -3745,13 +3745,13 @@
         <v>0</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0</v>
+        <v>0.00202</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>0</v>
+        <v>0.002021</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>0</v>
+        <v>0.002022</v>
       </c>
       <c r="P56" s="3" t="n">
         <v>0</v>
@@ -3779,7 +3779,7 @@
         <v>0</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>6.488324</v>
       </c>
       <c r="F57" s="3" t="n">
         <v>0</v>
@@ -6304,13 +6304,13 @@
         <v>-9.526535000000001</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>-0.8058650000000001</v>
+        <v>-1.520596</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>-0.340736</v>
+        <v>-0.41803</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>-0.505928</v>
+        <v>-0.389877</v>
       </c>
       <c r="L99" s="3" t="n">
         <v>-0.562889</v>
@@ -6319,7 +6319,7 @@
         <v>-1.202882</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>-2.331275</v>
+        <v>-2.316717</v>
       </c>
       <c r="O99" s="3" t="n">
         <v>80.00275000000001</v>
@@ -28750,7 +28750,11 @@
           <t>Deferred income tax (recovery)</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -31849,7 +31853,11 @@
           <t>Deferred income tax recovery (Note 14)</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -33057,7 +33065,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -34057,7 +34069,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -41582,7 +41598,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E331" t="inlineStr">
         <is>
           <t>-</t>
@@ -42782,7 +42802,11 @@
           <t>Loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
           <t>-</t>
@@ -63262,7 +63286,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D547" t="inlineStr"/>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E547" t="inlineStr">
         <is>
           <t>-</t>
@@ -65361,7 +65389,11 @@
           <t>Deferred income tax recovery (Note 14)</t>
         </is>
       </c>
-      <c r="D568" t="inlineStr"/>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E568" t="inlineStr">
         <is>
           <t>-</t>
@@ -71694,7 +71726,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D631" t="inlineStr"/>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E631" t="inlineStr">
         <is>
           <t>-</t>
@@ -72789,7 +72825,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D642" t="inlineStr"/>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E642" t="inlineStr">
         <is>
           <t>-</t>
@@ -72888,7 +72928,11 @@
           <t>Income from discontinued operations (Note 10)</t>
         </is>
       </c>
-      <c r="D643" t="inlineStr"/>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E643" t="inlineStr">
         <is>
           <t>-</t>
